--- a/data/rateBuildUp/File1/RPT_RPT8107702707903CZ_rateBuildUp.xlsx
+++ b/data/rateBuildUp/File1/RPT_RPT8107702707903CZ_rateBuildUp.xlsx
@@ -31103,7 +31103,7 @@
         <v>1394.186185838779</v>
       </c>
       <c r="CZ150" s="420" t="n">
-        <v>1434.632595321702</v>
+        <v>1434.632595321703</v>
       </c>
       <c r="DA150" s="421" t="n">
         <v>1411.599620741493</v>
@@ -35332,7 +35332,7 @@
         <v>3876.1025328176</v>
       </c>
       <c r="AY176" s="208" t="n">
-        <v>4724.0566381556</v>
+        <v>4724.056638155601</v>
       </c>
       <c r="BA176" s="155" t="inlineStr">
         <is>
@@ -39712,19 +39712,19 @@
         <v>4447.405947447092</v>
       </c>
       <c r="AU194" s="207" t="n">
-        <v>1315.118437055402</v>
+        <v>1315.118437055401</v>
       </c>
       <c r="AV194" s="207" t="n">
         <v>2630.740147270629</v>
       </c>
       <c r="AW194" s="207" t="n">
-        <v>3198.486606874324</v>
+        <v>3198.486606874323</v>
       </c>
       <c r="AX194" s="207" t="n">
         <v>3876.10253281807</v>
       </c>
       <c r="AY194" s="208" t="n">
-        <v>4724.056638154734</v>
+        <v>4724.056638154733</v>
       </c>
       <c r="BA194" s="155" t="inlineStr">
         <is>
@@ -39863,10 +39863,10 @@
         <v>0.7206607376657667</v>
       </c>
       <c r="CZ194" s="133" t="n">
-        <v>0.7166961054816515</v>
+        <v>0.7166961054816514</v>
       </c>
       <c r="DA194" s="134" t="n">
-        <v>0.6921691272136924</v>
+        <v>0.6921691272136923</v>
       </c>
     </row>
     <row r="195" ht="15.75" customHeight="1" thickBot="1">
@@ -42046,7 +42046,7 @@
         <v>3001.32233845578</v>
       </c>
       <c r="AX203" s="207" t="n">
-        <v>3649.277435723461</v>
+        <v>3649.277435723462</v>
       </c>
       <c r="AY203" s="208" t="n">
         <v>4475.701430532295</v>
@@ -42084,7 +42084,7 @@
         <v>19.34096219998492</v>
       </c>
       <c r="BK203" s="214" t="n">
-        <v>28.29548308520569</v>
+        <v>28.29548308520568</v>
       </c>
       <c r="BL203" s="222" t="n">
         <v>1258.270533532866</v>
@@ -42099,7 +42099,7 @@
         <v>3649.277435723463</v>
       </c>
       <c r="BP203" s="214" t="n">
-        <v>4475.701430532297</v>
+        <v>4475.701430532298</v>
       </c>
       <c r="BR203" s="155" t="inlineStr">
         <is>
@@ -43951,40 +43951,40 @@
         <v>197.1642684182779</v>
       </c>
       <c r="AN212" s="207" t="n">
-        <v>226.8250970950172</v>
+        <v>226.8250970950171</v>
       </c>
       <c r="AO212" s="208" t="n">
         <v>248.3552076227965</v>
       </c>
       <c r="AP212" s="500" t="n">
-        <v>0.0452133147537153</v>
+        <v>0.04521331475371532</v>
       </c>
       <c r="AQ212" s="501" t="n">
         <v>0.05042194755366478</v>
       </c>
       <c r="AR212" s="501" t="n">
-        <v>0.06563334335551543</v>
+        <v>0.06563334335551545</v>
       </c>
       <c r="AS212" s="501" t="n">
         <v>0.06350865520474974</v>
       </c>
       <c r="AT212" s="502" t="n">
-        <v>0.05856210284897486</v>
+        <v>0.05856210284897488</v>
       </c>
       <c r="AU212" s="501" t="n">
-        <v>0.0432264516419787</v>
+        <v>0.04322645164197871</v>
       </c>
       <c r="AV212" s="501" t="n">
         <v>0.04743058190033844</v>
       </c>
       <c r="AW212" s="501" t="n">
-        <v>0.06164298702846655</v>
+        <v>0.06164298702846656</v>
       </c>
       <c r="AX212" s="501" t="n">
-        <v>0.05851885887293774</v>
+        <v>0.05851885887293773</v>
       </c>
       <c r="AY212" s="502" t="n">
-        <v>0.05257244496539453</v>
+        <v>0.05257244496539454</v>
       </c>
       <c r="BA212" s="155" t="inlineStr">
         <is>
@@ -44007,31 +44007,31 @@
         <v>248.355207622</v>
       </c>
       <c r="BG212" s="503" t="n">
-        <v>0.04521331475370453</v>
+        <v>0.04521331475370454</v>
       </c>
       <c r="BH212" s="504" t="n">
-        <v>0.05042194755366496</v>
+        <v>0.05042194755366495</v>
       </c>
       <c r="BI212" s="504" t="n">
-        <v>0.06563334335552089</v>
+        <v>0.0656333433555209</v>
       </c>
       <c r="BJ212" s="504" t="n">
-        <v>0.06350865520474305</v>
+        <v>0.06350865520474304</v>
       </c>
       <c r="BK212" s="505" t="n">
-        <v>0.05856210284897043</v>
+        <v>0.05856210284897044</v>
       </c>
       <c r="BL212" s="504" t="n">
         <v>0.04322645164208252</v>
       </c>
       <c r="BM212" s="504" t="n">
-        <v>0.0474305819000999</v>
+        <v>0.04743058190009989</v>
       </c>
       <c r="BN212" s="504" t="n">
-        <v>0.06164298702838478</v>
+        <v>0.06164298702838479</v>
       </c>
       <c r="BO212" s="504" t="n">
-        <v>0.05851885887292714</v>
+        <v>0.05851885887292713</v>
       </c>
       <c r="BP212" s="505" t="n">
         <v>0.05257244496522195</v>
@@ -45517,13 +45517,13 @@
         <v>174399.7251953768</v>
       </c>
       <c r="AM223" s="408" t="n">
-        <v>265497.3076408402</v>
+        <v>265497.3076408403</v>
       </c>
       <c r="AN223" s="408" t="n">
         <v>310685.3563988484</v>
       </c>
       <c r="AO223" s="409" t="n">
-        <v>361266.5879902403</v>
+        <v>361266.5879902404</v>
       </c>
       <c r="AP223" s="436" t="n">
         <v>1358.792448141342</v>
@@ -45532,7 +45532,7 @@
         <v>1314.765281734809</v>
       </c>
       <c r="AR223" s="437" t="n">
-        <v>1264.710304505289</v>
+        <v>1264.71030450529</v>
       </c>
       <c r="AS223" s="437" t="n">
         <v>1262.096640327373</v>
@@ -45552,13 +45552,13 @@
         <v>174399.7251953768</v>
       </c>
       <c r="BD223" s="440" t="n">
-        <v>265497.3076408402</v>
+        <v>265497.3076408403</v>
       </c>
       <c r="BE223" s="440" t="n">
         <v>310685.3563988484</v>
       </c>
       <c r="BF223" s="441" t="n">
-        <v>361266.5879902403</v>
+        <v>361266.5879902404</v>
       </c>
       <c r="BG223" s="442" t="n">
         <v>1358.792448141342</v>
@@ -45567,7 +45567,7 @@
         <v>1314.765281734809</v>
       </c>
       <c r="BI223" s="443" t="n">
-        <v>1264.710304505289</v>
+        <v>1264.71030450529</v>
       </c>
       <c r="BJ223" s="443" t="n">
         <v>1262.096640327373</v>
@@ -48415,13 +48415,13 @@
         <v>174399.7251953768</v>
       </c>
       <c r="AM241" s="408" t="n">
-        <v>265497.3076408402</v>
+        <v>265497.3076408403</v>
       </c>
       <c r="AN241" s="408" t="n">
         <v>310685.3563988484</v>
       </c>
       <c r="AO241" s="409" t="n">
-        <v>361266.5879902403</v>
+        <v>361266.5879902404</v>
       </c>
       <c r="AP241" s="436" t="n">
         <v>1358.792448141342</v>
@@ -48430,7 +48430,7 @@
         <v>1314.765281734809</v>
       </c>
       <c r="AR241" s="437" t="n">
-        <v>1264.710304505289</v>
+        <v>1264.71030450529</v>
       </c>
       <c r="AS241" s="437" t="n">
         <v>1262.096640327373</v>
@@ -48450,13 +48450,13 @@
         <v>174399.7251953768</v>
       </c>
       <c r="BD241" s="440" t="n">
-        <v>265497.3076408402</v>
+        <v>265497.3076408403</v>
       </c>
       <c r="BE241" s="440" t="n">
         <v>310685.3563988484</v>
       </c>
       <c r="BF241" s="441" t="n">
-        <v>361266.5879902403</v>
+        <v>361266.5879902404</v>
       </c>
       <c r="BG241" s="442" t="n">
         <v>1358.792448141342</v>
@@ -48465,7 +48465,7 @@
         <v>1314.765281734809</v>
       </c>
       <c r="BI241" s="443" t="n">
-        <v>1264.710304505289</v>
+        <v>1264.71030450529</v>
       </c>
       <c r="BJ241" s="443" t="n">
         <v>1262.096640327373</v>
@@ -49755,7 +49755,7 @@
         <v>2128190.937105205</v>
       </c>
       <c r="AL250" s="408" t="n">
-        <v>3947468.179799807</v>
+        <v>3947468.179799806</v>
       </c>
       <c r="AM250" s="408" t="n">
         <v>4734892.634092139</v>
@@ -49790,7 +49790,7 @@
         <v>2128190.937105205</v>
       </c>
       <c r="BC250" s="440" t="n">
-        <v>3947468.179799807</v>
+        <v>3947468.179799806</v>
       </c>
       <c r="BD250" s="440" t="n">
         <v>4734892.634092139</v>
@@ -53013,7 +53013,7 @@
         <v>2128190.937105205</v>
       </c>
       <c r="AL268" s="408" t="n">
-        <v>3947468.179799807</v>
+        <v>3947468.179799806</v>
       </c>
       <c r="AM268" s="408" t="n">
         <v>4734892.634092139</v>
@@ -53048,7 +53048,7 @@
         <v>2128190.937105205</v>
       </c>
       <c r="BC268" s="440" t="n">
-        <v>3947468.179799807</v>
+        <v>3947468.179799806</v>
       </c>
       <c r="BD268" s="440" t="n">
         <v>4734892.634092139</v>
@@ -55206,7 +55206,7 @@
         <v>141.6497440296129</v>
       </c>
       <c r="AY280" s="208" t="n">
-        <v>143.9115807488387</v>
+        <v>143.9115807488388</v>
       </c>
       <c r="BA280" s="155" t="inlineStr">
         <is>
@@ -55256,7 +55256,7 @@
         <v>141.6497440296129</v>
       </c>
       <c r="BP280" s="214" t="n">
-        <v>143.9115807488387</v>
+        <v>143.9115807488388</v>
       </c>
       <c r="BR280" s="155" t="inlineStr">
         <is>
@@ -59513,7 +59513,7 @@
         <v>141.6497440296129</v>
       </c>
       <c r="AY298" s="208" t="n">
-        <v>143.9115807488387</v>
+        <v>143.9115807488388</v>
       </c>
       <c r="BA298" s="155" t="inlineStr">
         <is>
@@ -59563,7 +59563,7 @@
         <v>141.6497440296129</v>
       </c>
       <c r="BP298" s="214" t="n">
-        <v>143.9115807488387</v>
+        <v>143.9115807488388</v>
       </c>
       <c r="BR298" s="155" t="inlineStr">
         <is>
@@ -59652,10 +59652,10 @@
         <v>0.7206607376657667</v>
       </c>
       <c r="CZ298" s="212" t="n">
-        <v>0.7166961054816515</v>
+        <v>0.7166961054816514</v>
       </c>
       <c r="DA298" s="213" t="n">
-        <v>0.6921691272136924</v>
+        <v>0.6921691272136923</v>
       </c>
     </row>
     <row r="299" ht="15.75" customHeight="1" thickBot="1">
@@ -61457,7 +61457,7 @@
         <v>124.6916206509199</v>
       </c>
       <c r="AY307" s="208" t="n">
-        <v>126.2407733170468</v>
+        <v>126.2407733170467</v>
       </c>
       <c r="BA307" s="155" t="inlineStr">
         <is>
@@ -61507,7 +61507,7 @@
         <v>124.6916206509199</v>
       </c>
       <c r="BP307" s="214" t="n">
-        <v>126.2407733170468</v>
+        <v>126.2407733170467</v>
       </c>
       <c r="BR307" s="155" t="inlineStr">
         <is>
@@ -69162,7 +69162,7 @@
         <v>2842.312675205743</v>
       </c>
       <c r="AS354" s="437" t="n">
-        <v>2527.356565481374</v>
+        <v>2527.356565481375</v>
       </c>
       <c r="AT354" s="438" t="n">
         <v>2679.627516824331</v>
@@ -69197,7 +69197,7 @@
         <v>2842.312675205743</v>
       </c>
       <c r="BJ354" s="443" t="n">
-        <v>2527.356565481374</v>
+        <v>2527.356565481375</v>
       </c>
       <c r="BK354" s="444" t="n">
         <v>2679.627516824331</v>
@@ -71905,7 +71905,7 @@
         <v>2842.312675205743</v>
       </c>
       <c r="AS372" s="437" t="n">
-        <v>2527.356565481374</v>
+        <v>2527.356565481375</v>
       </c>
       <c r="AT372" s="438" t="n">
         <v>2679.627516824331</v>
@@ -71940,7 +71940,7 @@
         <v>2842.312675205743</v>
       </c>
       <c r="BJ372" s="443" t="n">
-        <v>2527.356565481374</v>
+        <v>2527.356565481375</v>
       </c>
       <c r="BK372" s="444" t="n">
         <v>2679.627516824331</v>
@@ -71993,7 +71993,7 @@
         <v>1434.632599798829</v>
       </c>
       <c r="DA372" s="421" t="n">
-        <v>1411.599632113797</v>
+        <v>1411.599632113798</v>
       </c>
     </row>
     <row r="375">
